--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -857,21 +857,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -890,9 +887,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1234,228 +1228,252 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="13"/>
+      <c r="L8" s="11"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="12" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="13"/>
+      <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="12" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="13"/>
+      <c r="L10" s="11"/>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:6">
+      <c r="A14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
-    <t>对账单</t>
+    <t>{titil}</t>
   </si>
   <si>
     <t>供应商：</t>
@@ -155,7 +155,7 @@
     <t>开户行：</t>
   </si>
   <si>
-    <t>{.bankSubbranch}</t>
+    <t>{bankSubbranch}</t>
   </si>
   <si>
     <t>账户名称：</t>
@@ -857,7 +857,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -876,6 +876,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -887,6 +890,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1212,16 +1218,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="2" max="3" width="16.875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10.375" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="5" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="12.625" customWidth="1"/>
     <col min="8" max="8" width="13.25" customWidth="1"/>
     <col min="9" max="9" width="10.375" customWidth="1"/>
     <col min="10" max="10" width="14.875" customWidth="1"/>
     <col min="11" max="11" width="12.875" customWidth="1"/>
-    <col min="12" max="12" width="10.375" customWidth="1"/>
+    <col min="12" max="12" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" spans="6:8">
@@ -1333,7 +1339,7 @@
       <c r="E7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="5" t="s">
@@ -1351,66 +1357,66 @@
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="10" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="11"/>
+      <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="10" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="10" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1422,7 +1428,7 @@
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1434,7 +1440,7 @@
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1446,7 +1452,7 @@
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="3" t="s">

--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>{titil}</t>
   </si>
@@ -62,6 +62,9 @@
     <t>采购订单</t>
   </si>
   <si>
+    <t>送货单号</t>
+  </si>
+  <si>
     <t>单据单号</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
   </si>
   <si>
     <t>{.poCode}</t>
+  </si>
+  <si>
+    <t>{.deliveryCode}</t>
   </si>
   <si>
     <t>{.sourceCode}</t>
@@ -857,7 +863,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -890,9 +896,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -962,6 +965,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1214,30 +1224,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="3" width="16.875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="9" width="10.375" customWidth="1"/>
-    <col min="10" max="10" width="14.875" customWidth="1"/>
-    <col min="11" max="11" width="12.875" customWidth="1"/>
-    <col min="12" max="12" width="18.5" customWidth="1"/>
+    <col min="2" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="11" width="14.875" customWidth="1"/>
+    <col min="12" max="12" width="12.875" customWidth="1"/>
+    <col min="13" max="13" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="6:8">
-      <c r="F1" s="1" t="s">
+    <row r="1" ht="18.75" spans="7:9">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1248,8 +1258,9 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1260,8 +1271,9 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1272,8 +1284,9 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1284,8 +1297,9 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -1322,48 +1336,54 @@
       <c r="L6" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="M6" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="G7" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="11" t="s">
         <v>32</v>
       </c>
+      <c r="L7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1374,14 +1394,15 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-      <c r="K8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="13"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="12"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1392,14 +1413,15 @@
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
-      <c r="K9" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="13"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="12"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -1409,77 +1431,82 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="13"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="12"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -68,7 +68,7 @@
     <t>单据单号</t>
   </si>
   <si>
-    <t>确认日期</t>
+    <t>单据日期</t>
   </si>
   <si>
     <t>物料编码</t>
@@ -107,7 +107,7 @@
     <t>{.sourceCode}</t>
   </si>
   <si>
-    <t>{.confirmDate}</t>
+    <t>{.date}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -965,13 +965,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>{titil}</t>
   </si>
@@ -38,25 +38,40 @@
     <t>{supplierName}</t>
   </si>
   <si>
+    <t>客户：</t>
+  </si>
+  <si>
+    <t>东莞市简拍智造科技有限公司</t>
+  </si>
+  <si>
     <t>联系人：</t>
   </si>
   <si>
     <t>{contactName}</t>
   </si>
   <si>
+    <t>{poFollowerName}</t>
+  </si>
+  <si>
     <t>联系方式：</t>
   </si>
   <si>
     <t>{contactTelNumber}</t>
   </si>
   <si>
-    <t>结算方式：</t>
-  </si>
-  <si>
-    <t>{settleDictName}</t>
-  </si>
-  <si>
-    <t>序号</t>
+    <t>{poFollowerTelNumber}</t>
+  </si>
+  <si>
+    <t>付款条件：</t>
+  </si>
+  <si>
+    <t>{paymentConditionName}</t>
+  </si>
+  <si>
+    <t>单据日期</t>
+  </si>
+  <si>
+    <t>单据单号</t>
   </si>
   <si>
     <t>采购订单</t>
@@ -65,28 +80,25 @@
     <t>送货单号</t>
   </si>
   <si>
-    <t>单据单号</t>
-  </si>
-  <si>
-    <t>单据日期</t>
-  </si>
-  <si>
     <t>物料编码</t>
   </si>
   <si>
     <t>名称</t>
   </si>
   <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>单价</t>
-  </si>
-  <si>
-    <t>税率</t>
+    <t>出货数量</t>
+  </si>
+  <si>
+    <t>含税单价</t>
+  </si>
+  <si>
+    <t>折扣率</t>
+  </si>
+  <si>
+    <t>折扣额</t>
+  </si>
+  <si>
+    <t>预付金额</t>
   </si>
   <si>
     <t>金额（含税）</t>
@@ -95,7 +107,10 @@
     <t>备注</t>
   </si>
   <si>
-    <t>{.index}</t>
+    <t>{.date}</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
   </si>
   <si>
     <t>{.poCode}</t>
@@ -104,28 +119,25 @@
     <t>{.deliveryCode}</t>
   </si>
   <si>
-    <t>{.sourceCode}</t>
-  </si>
-  <si>
-    <t>{.date}</t>
-  </si>
-  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.unitName}</t>
-  </si>
-  <si>
     <t>{.qty}</t>
   </si>
   <si>
     <t>{.taxPrice}</t>
   </si>
   <si>
-    <t>{.taxRateStr}</t>
+    <t>{.discountRateStr}</t>
+  </si>
+  <si>
+    <t>{.discountAmount}</t>
+  </si>
+  <si>
+    <t>{.prepayAmount}</t>
   </si>
   <si>
     <t>{.taxAmount}</t>
@@ -863,7 +875,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -894,14 +906,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1220,163 +1241,190 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="12.625" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="3" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="13.25" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="15.125" customWidth="1"/>
     <col min="11" max="11" width="14.875" customWidth="1"/>
-    <col min="12" max="12" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="7:9">
-      <c r="G1" s="1" t="s">
+    <row r="1" ht="18.75" spans="1:13">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="K2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="12"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="K3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="12"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="K4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="12"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1388,14 +1436,14 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="12"/>
+      <c r="L8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="14"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1407,99 +1455,99 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="12"/>
+      <c r="L9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="14"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" s="12"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="14"/>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="3"/>
+    <row r="12" spans="1:9">
+      <c r="A12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="I12" s="12"/>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="3"/>
+    <row r="13" spans="1:6">
+      <c r="A13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="3"/>
+    <row r="14" spans="1:6">
+      <c r="A14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="3"/>
+    <row r="15" spans="1:6">
+      <c r="A15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="C5:F5"/>
     <mergeCell ref="A8:K8"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="L10:M10"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>{titil}</t>
   </si>
@@ -140,7 +140,7 @@
     <t>{.prepayAmount}</t>
   </si>
   <si>
-    <t>{.taxAmount}</t>
+    <t>{.discountTaxAmount}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -149,16 +149,25 @@
     <t>出货小计</t>
   </si>
   <si>
+    <t>{totalDeliveryQty}</t>
+  </si>
+  <si>
     <t>{totalDeliveryAmount}</t>
   </si>
   <si>
     <t>退料小计</t>
   </si>
   <si>
+    <t>{totalReceiveQty}</t>
+  </si>
+  <si>
     <t>{totalReceiveAmount}</t>
   </si>
   <si>
     <t>合计应付款</t>
+  </si>
+  <si>
+    <t>{totalQty}</t>
   </si>
   <si>
     <t>{totalAmount}</t>
@@ -875,7 +884,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -897,35 +906,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1245,12 +1242,12 @@
     <col min="3" max="4" width="16.875" customWidth="1"/>
     <col min="5" max="5" width="17.875" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="16.25" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15.125" customWidth="1"/>
     <col min="11" max="11" width="14.875" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="12" width="21.875" customWidth="1"/>
     <col min="13" max="13" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1426,66 +1423,72 @@
       <c r="A8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="13" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="14"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" s="10"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="M9" s="14"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="10"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="A10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="H10" s="10"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="14"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="10"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1494,11 +1497,11 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1506,11 +1509,11 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1518,18 +1521,18 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="15">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="L2:M2"/>
@@ -1538,12 +1541,9 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="C5:F5"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>

--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
     <t>单据日期</t>
   </si>
   <si>
-    <t>单据单号</t>
+    <t>单据编号</t>
   </si>
   <si>
     <t>采购订单</t>
@@ -897,6 +897,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -920,9 +923,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1282,10 +1282,10 @@
       <c r="K2" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="12"/>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
@@ -1301,10 +1301,10 @@
       <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="12"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
@@ -1320,12 +1320,12 @@
       <c r="K4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="12"/>
+      <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1338,168 +1338,168 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10" t="s">
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="M8" s="10"/>
+      <c r="M8" s="11"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10" t="s">
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M9" s="10"/>
+      <c r="M9" s="11"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="10" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10" t="s">
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="11"/>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:13">
+      <c r="A12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="11"/>
+      <c r="B12" s="12"/>
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="I12" s="12"/>
+      <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:13">
+      <c r="A13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="3" t="s">
         <v>51</v>
       </c>
@@ -1507,11 +1507,11 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:13">
+      <c r="A14" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="12"/>
       <c r="C14" s="3" t="s">
         <v>53</v>
       </c>
@@ -1519,11 +1519,11 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:13">
+      <c r="A15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="11"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="3" t="s">
         <v>55</v>
       </c>

--- a/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/exportPoReconciliation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,7 @@
     <t>金额（含税）</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>采方备注</t>
   </si>
   <si>
     <t>{.date}</t>
@@ -143,7 +143,7 @@
     <t>{.discountTaxAmount}</t>
   </si>
   <si>
-    <t>{.remark}</t>
+    <t>{.purchaseRemark}</t>
   </si>
   <si>
     <t>出货小计</t>
